--- a/semantic_core_results.xlsx
+++ b/semantic_core_results.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статистика" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Семантическое ядро" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мягкая мебель" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кровати и матрасы" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шкафы и системы хранения" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мебель для хранения" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кровати и матрасы" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Столы и стулья" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -484,33 +484,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>13408</v>
+        <v>20769</v>
       </c>
       <c r="D5" t="n">
-        <v>295019</v>
+        <v>834702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>27675</v>
+        <v>13408</v>
       </c>
       <c r="D6" t="n">
-        <v>181586</v>
+        <v>295019</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1630,17 +1630,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>спальня мебель</t>
+          <t>стеллаж</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>50422</t>
+          <t>834702</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1651,17 +1651,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>постель это</t>
+          <t>полка в шкаф</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1672,17 +1672,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>кровати и матрасы</t>
+          <t>шкаф с полками</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1693,17 +1693,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>диван на кухню со спальным местом</t>
+          <t>шкаф с ящиками</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1714,17 +1714,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>м постель</t>
+          <t>мебель для хранения</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1735,17 +1735,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>купить кровать и матрас</t>
+          <t>стеллаж с ящиками</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1756,17 +1756,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>кровать с матрасом и ящиками</t>
+          <t>склад для хранения мебели</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1777,38 +1777,38 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>кровать с механизмом и матрасом</t>
+          <t>мебельная кухня</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>кровать с подъемным механизмом и матрасом</t>
+          <t>склад для хранения мебели москва</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>697</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1819,59 +1819,59 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bed</t>
+          <t>замок мебельный</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>295019</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>тахта кровать</t>
+          <t>место для хранения мебели</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>455</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>купить кровать с ящиками и матрас</t>
+          <t>бокс для хранения мебели</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>404</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1882,122 +1882,122 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>я хочу спать</t>
+          <t>полки в гардеробную</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>кровати диваны и матрасы</t>
+          <t>полки для гардеробной</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>односпальные кровати и матрасы</t>
+          <t>аренда для хранения мебели</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>кровать и матрас сайт</t>
+          <t>сейф мебельный</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>орматек кровать</t>
+          <t>мебель для хранения товаров</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>189</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>кровать и матрас 160х200</t>
+          <t>мебель для хранения стеллажи</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2008,80 +2008,80 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>детские кровати и матрасы</t>
+          <t>аренда для хранения мебели москва</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>484</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>хочу спать</t>
+          <t>помещение для хранения мебели</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>149668</t>
+          <t>603</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>купить кровать с матрасом и механизмом</t>
+          <t>мебель для хранения вещей</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>529</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>купить кровать с подъемным механизмом и матрасом</t>
+          <t>мебель для хранения тумба</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2092,38 +2092,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>диван раскладной на кухню со спальным местом</t>
+          <t>мебель для хранения купить</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>размеры кроватей и матрасов</t>
+          <t>мебель для хранения в детской</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2134,17 +2134,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>купить недорогие кровати и матрасы</t>
+          <t>мебель для хранения одежды</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>108</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2155,332 +2155,332 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>магазин кроватей и матрасов</t>
+          <t>контейнер для хранения мебели</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>457</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>деньги не спят</t>
+          <t>мебель для хранения предметов</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>425</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>кровать с подъемным механизмом и матрасом 160х200</t>
+          <t>лежит на шкафе</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>спальная мебель</t>
+          <t>гост мебель для хранения</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>детские кровати с матрасом и ящиками</t>
+          <t>склад для хранения мебели москва недорого</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>кровати и матрасы цена</t>
+          <t>склады для временного хранения мебели</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>кровать и матрас москве</t>
+          <t>мебель для хранения оборудования</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>296</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>диван кровать и ортопедическим матрасом</t>
+          <t>боксы для хранения мебели в москве</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>пастель или постель</t>
+          <t>аренда склада для хранения мебели</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>654</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>купить матрас 160х200 и кровать</t>
+          <t>мебель для хранения посуды</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>264</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>мебель кровати и матрасы</t>
+          <t>ящики для хранения мебели</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>спальные кровати и матрасы</t>
+          <t>теплый склад для хранения мебели</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>кровати и матрасы каталог и цены</t>
+          <t>корпусная мебель для хранения</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>кровать и матрас аскона</t>
+          <t>аренда склада для хранения мебели москва</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>орматек кровать купить</t>
+          <t>модульная мебель для хранения</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>кровати и матрасы отзывы</t>
+          <t>мебель для хранения белья</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2491,17 +2491,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>кровать диван с ящиками и матрасом</t>
+          <t>мебель для хранения в гостиной</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2512,17 +2512,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>матрас двуспальный и кровать</t>
+          <t>функциональная мебель для хранения</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>157</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2533,101 +2533,101 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>купить кровать и матрас в москве</t>
+          <t>система для хранения мебель</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ортопедическая кровать и матрас</t>
+          <t>склад для временного хранения мебели при переезде</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>192</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>кровати и матрасы официальный сайт</t>
+          <t>мебельные замки</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>мягкие матрасы и кровати</t>
+          <t>мебель для кухни для хранения</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>матрасы и основания кроватей</t>
+          <t>садовая мебель для хранения</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2638,59 +2638,59 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>кровать с изголовьем и матрасом</t>
+          <t>мебельная стенка</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Кровати и матрасы</t>
+          <t>Мебель для хранения</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>кровать односпальная с ящиками и матрасом</t>
+          <t>камера хранения для мебели</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>дом мебели</t>
+          <t>спальня мебель</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>181586</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2701,17 +2701,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>корпусная мебель</t>
+          <t>постель это</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>50792</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2722,17 +2722,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>мир мебели</t>
+          <t>кровати и матрасы</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -2743,17 +2743,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>мебель ру</t>
+          <t>диван на кухню со спальным местом</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -2764,17 +2764,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>стеллаж м</t>
+          <t>м постель</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -2785,17 +2785,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>шкафы и системы хранения</t>
+          <t>купить кровать и матрас</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -2806,17 +2806,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>корпусная мебель на заказ</t>
+          <t>кровать с матрасом и ящиками</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -2827,17 +2827,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>стеллаж это</t>
+          <t>кровать с механизмом и матрасом</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -2848,17 +2848,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>гардероб это</t>
+          <t>кровать с подъемным механизмом и матрасом</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -2869,164 +2869,164 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>корпусная мебель это</t>
+          <t>bed</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>295019</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>шкафчик</t>
+          <t>тахта кровать</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>175660</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>стелажи или стеллажи купить</t>
+          <t>купить кровать с ящиками и матрас</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>я хочу спать</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>78664</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>антресоль это</t>
+          <t>кровати диваны и матрасы</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>872</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>шифоньер это</t>
+          <t>односпальные кровати и матрасы</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>854</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>в гардеробах оборудуют места исходя из площади</t>
+          <t>кровать и матрас сайт</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>851</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>сервант это</t>
+          <t>орматек кровать</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3037,101 +3037,101 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>как выбрать удобную мебель для балкона</t>
+          <t>кровать и матрас 160х200</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>786</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>стелаж или стеллаж как правильно</t>
+          <t>детские кровати и матрасы</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>751</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>шифонер или шифоньер как правильно написать</t>
+          <t>хочу спать</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>149668</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Шкафы и системы хранения</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>мебелировка</t>
+          <t>купить кровать с матрасом и механизмом</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>638</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>столы и стулья</t>
+          <t>купить кровать с подъемным механизмом и матрасом</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>147330</t>
+          <t>628</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -3142,38 +3142,38 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>кухня мебель</t>
+          <t>диван раскладной на кухню со спальным местом</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>123992</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>купить столик</t>
+          <t>размеры кроватей и матрасов</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>79756</t>
+          <t>590</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -3184,17 +3184,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>купить стол и стулья</t>
+          <t>купить недорогие кровати и матрасы</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>589</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -3205,17 +3205,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>столы и стулья рядом</t>
+          <t>магазин кроватей и матрасов</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>555</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -3226,80 +3226,80 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>столы и стулья 7</t>
+          <t>деньги не спят</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>стол и 2 стула</t>
+          <t>кровать с подъемным механизмом и матрасом 160х200</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>41936</t>
+          <t>502</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>круглый стол и стулья</t>
+          <t>спальная мебель</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>36719</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>кухонный стол и стулья</t>
+          <t>детские кровати с матрасом и ящиками</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -3310,17 +3310,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>порядок стол и стулья</t>
+          <t>кровати и матрасы цена</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -3331,17 +3331,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>мебель столы и стулья</t>
+          <t>кровать и матрас москве</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -3352,17 +3352,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>детский стол и стул</t>
+          <t>диван кровать и ортопедическим матрасом</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3373,38 +3373,38 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>столы и стулья 5</t>
+          <t>пастель или постель</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ами мебель кровать</t>
+          <t>купить матрас 160х200 и кровать</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>359</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -3415,17 +3415,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>столы и стулья сайт</t>
+          <t>мебель кровати и матрасы</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>354</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -3436,101 +3436,101 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>круглый стол и 2 стула</t>
+          <t>спальные кровати и матрасы</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>336</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>стол и стул 2 в 1</t>
+          <t>кровати и матрасы каталог и цены</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>786</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>купить кухонный стол и стулья</t>
+          <t>кровать и матрас аскона</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>столы и стулья 21</t>
+          <t>орматек кровать купить</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>обеденные столы и стулья</t>
+          <t>кровати и матрасы отзывы</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>291</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -3541,17 +3541,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>комната стул и стол</t>
+          <t>кровать диван с ящиками и матрасом</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>291</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -3562,101 +3562,101 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>комплект стол и стулья</t>
+          <t>матрас двуспальный и кровать</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>стол и стулья для кухни</t>
+          <t>купить кровать и матрас в москве</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>столы и стулья маленькие</t>
+          <t>ортопедическая кровать и матрас</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>столы и стулья магазин</t>
+          <t>кровати и матрасы официальный сайт</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>820</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>деревянные столы и стулья</t>
+          <t>мягкие матрасы и кровати</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>274</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -3667,17 +3667,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>столы и стулья большие</t>
+          <t>матрасы и основания кроватей</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>265</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3688,17 +3688,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>диваны столы и стулья</t>
+          <t>кровать с изголовьем и матрасом</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>257</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -3709,21 +3709,21 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Столы и стулья</t>
+          <t>Кровати и матрасы</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>кресла и столы стулья</t>
+          <t>кровать односпальная с ящиками и матрасом</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>612</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E151" t="inlineStr"/>
     </row>
@@ -3735,12 +3735,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>стол и стул для детей</t>
+          <t>столы и стулья</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>147330</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -3756,16 +3756,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>выполните стол и стул</t>
+          <t>кухня мебель</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>123992</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr"/>
     </row>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>столы и стулья москва</t>
+          <t>купить столик</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>79756</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>столик для дивана</t>
+          <t>купить стол и стулья</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>стол и стулья недорогие</t>
+          <t>столы и стулья рядом</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -3840,16 +3840,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>стол и 4 стула</t>
+          <t>столы и стулья 7</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E157" t="inlineStr"/>
     </row>
@@ -3861,16 +3861,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>столы и стулья официальный сайт</t>
+          <t>стол и 2 стула</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E158" t="inlineStr"/>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>стоит стол и стулья</t>
+          <t>круглый стол и стулья</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>столы и стулья бу</t>
+          <t>кухонный стол и стулья</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -3924,16 +3924,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>стол стул и шкаф</t>
+          <t>порядок стол и стулья</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>34043</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E161" t="inlineStr"/>
     </row>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>кухня мебель дизайн</t>
+          <t>мебель столы и стулья</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -3966,16 +3966,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>стол и 8 стульев</t>
+          <t>детский стол и стул</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E163" t="inlineStr"/>
     </row>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>купить детский стол и стул</t>
+          <t>столы и стулья 5</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>столы и стулья для кафе</t>
+          <t>ами мебель кровать</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -4029,16 +4029,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>купить стол и стулья для кухни</t>
+          <t>столы и стулья сайт</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr"/>
     </row>
@@ -4050,16 +4050,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>столы и стулья официальный</t>
+          <t>круглый стол и 2 стула</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E167" t="inlineStr"/>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>столы и стулья из дерева</t>
+          <t>стол и стул 2 в 1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -4092,16 +4092,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>стол и 6 стульев</t>
+          <t>купить кухонный стол и стулья</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E169" t="inlineStr"/>
     </row>
@@ -4113,16 +4113,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>мебель донецк</t>
+          <t>столы и стулья 21</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E170" t="inlineStr"/>
     </row>
@@ -4134,16 +4134,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>новые столы и стулья</t>
+          <t>обеденные столы и стулья</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E171" t="inlineStr"/>
     </row>
@@ -4155,18 +4155,627 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
+          <t>комната стул и стол</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>комплект стол и стулья</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>стол и стулья для кухни</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>столы и стулья маленькие</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2956</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>столы и стулья магазин</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>деревянные столы и стулья</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2518</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>столы и стулья большие</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>диваны столы и стулья</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>кресла и столы стулья</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>стол и стул для детей</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>выполните стол и стул</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>6771</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>столы и стулья москва</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>столик для дивана</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>стол и стулья недорогие</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>стол и 4 стула</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>столы и стулья официальный сайт</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>4320</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>стоит стол и стулья</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>столы и стулья бу</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>стол стул и шкаф</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>кухня мебель дизайн</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>стол и 8 стульев</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>купить детский стол и стул</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>столы и стулья для кафе</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>купить стол и стулья для кухни</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>столы и стулья официальный</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>4947</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>столы и стулья из дерева</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>стол и 6 стульев</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>мебель донецк</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>17195</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>новые столы и стулья</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Столы и стулья</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
           <t>стол и стулья б</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>1236</t>
         </is>
       </c>
-      <c r="D172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" t="inlineStr"/>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4993,12 +5602,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>спальня мебель</t>
+          <t>стеллаж</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50422</t>
+          <t>834702</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5008,12 +5617,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>постель это</t>
+          <t>полка в шкаф</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5023,12 +5632,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>кровати и матрасы</t>
+          <t>шкаф с полками</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5038,12 +5647,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>диван на кухню со спальным местом</t>
+          <t>шкаф с ящиками</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5053,12 +5662,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>м постель</t>
+          <t>мебель для хранения</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5068,12 +5677,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>купить кровать и матрас</t>
+          <t>стеллаж с ящиками</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5083,12 +5692,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>кровать с матрасом и ящиками</t>
+          <t>склад для хранения мебели</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5098,27 +5707,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>кровать с механизмом и матрасом</t>
+          <t>мебельная кухня</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>кровать с подъемным механизмом и матрасом</t>
+          <t>склад для хранения мебели москва</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>697</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5128,42 +5737,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bed</t>
+          <t>замок мебельный</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>295019</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>тахта кровать</t>
+          <t>место для хранения мебели</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>455</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>купить кровать с ящиками и матрас</t>
+          <t>бокс для хранения мебели</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5173,87 +5782,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>я хочу спать</t>
+          <t>полки в гардеробную</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>кровати диваны и матрасы</t>
+          <t>полки для гардеробной</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>односпальные кровати и матрасы</t>
+          <t>аренда для хранения мебели</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>кровать и матрас сайт</t>
+          <t>сейф мебельный</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>орматек кровать</t>
+          <t>мебель для хранения товаров</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>кровать и матрас 160х200</t>
+          <t>мебель для хранения стеллажи</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>183</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5263,57 +5872,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>детские кровати и матрасы</t>
+          <t>аренда для хранения мебели москва</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>484</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>хочу спать</t>
+          <t>помещение для хранения мебели</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>149668</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>купить кровать с матрасом и механизмом</t>
+          <t>мебель для хранения вещей</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>529</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>купить кровать с подъемным механизмом и матрасом</t>
+          <t>мебель для хранения тумба</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>119</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5323,27 +5932,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>диван раскладной на кухню со спальным местом</t>
+          <t>мебель для хранения купить</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>117</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>размеры кроватей и матрасов</t>
+          <t>мебель для хранения в детской</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5353,12 +5962,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>купить недорогие кровати и матрасы</t>
+          <t>мебель для хранения одежды</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5368,237 +5977,237 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>магазин кроватей и матрасов</t>
+          <t>контейнер для хранения мебели</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>457</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>деньги не спят</t>
+          <t>мебель для хранения предметов</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>425</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>кровать с подъемным механизмом и матрасом 160х200</t>
+          <t>лежит на шкафе</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>спальная мебель</t>
+          <t>гост мебель для хранения</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>детские кровати с матрасом и ящиками</t>
+          <t>склад для хранения мебели москва недорого</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>кровати и матрасы цена</t>
+          <t>склады для временного хранения мебели</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>223</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>кровать и матрас москве</t>
+          <t>мебель для хранения оборудования</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>диван кровать и ортопедическим матрасом</t>
+          <t>боксы для хранения мебели в москве</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>178</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>пастель или постель</t>
+          <t>аренда склада для хранения мебели</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>654</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>купить матрас 160х200 и кровать</t>
+          <t>мебель для хранения посуды</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>264</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>мебель кровати и матрасы</t>
+          <t>ящики для хранения мебели</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>252</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>спальные кровати и матрасы</t>
+          <t>теплый склад для хранения мебели</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>кровати и матрасы каталог и цены</t>
+          <t>корпусная мебель для хранения</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>кровать и матрас аскона</t>
+          <t>аренда склада для хранения мебели москва</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>322</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>орматек кровать купить</t>
+          <t>модульная мебель для хранения</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>кровати и матрасы отзывы</t>
+          <t>мебель для хранения белья</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5608,12 +6217,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>кровать диван с ящиками и матрасом</t>
+          <t>мебель для хранения в гостиной</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5623,12 +6232,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>матрас двуспальный и кровать</t>
+          <t>функциональная мебель для хранения</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5638,72 +6247,72 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>купить кровать и матрас в москве</t>
+          <t>система для хранения мебель</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ортопедическая кровать и матрас</t>
+          <t>склад для временного хранения мебели при переезде</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>кровати и матрасы официальный сайт</t>
+          <t>мебельные замки</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>мягкие матрасы и кровати</t>
+          <t>мебель для кухни для хранения</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>матрасы и основания кроватей</t>
+          <t>садовая мебель для хранения</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5713,31 +6322,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>кровать с изголовьем и матрасом</t>
+          <t>мебельная стенка</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>кровать односпальная с ящиками и матрасом</t>
+          <t>камера хранения для мебели</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -5751,10 +6360,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -5779,12 +6388,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>дом мебели</t>
+          <t>спальня мебель</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>181586</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5794,12 +6403,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>корпусная мебель</t>
+          <t>постель это</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50792</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5809,12 +6418,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>мир мебели</t>
+          <t>кровати и матрасы</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5824,12 +6433,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>мебель ру</t>
+          <t>диван на кухню со спальным местом</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5839,12 +6448,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>стеллаж м</t>
+          <t>м постель</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5854,12 +6463,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>шкафы и системы хранения</t>
+          <t>купить кровать и матрас</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5869,12 +6478,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>корпусная мебель на заказ</t>
+          <t>кровать с матрасом и ящиками</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5884,12 +6493,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>стеллаж это</t>
+          <t>кровать с механизмом и матрасом</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5899,12 +6508,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>гардероб это</t>
+          <t>кровать с подъемным механизмом и матрасом</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5914,117 +6523,117 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>корпусная мебель это</t>
+          <t>bed</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>295019</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>шкафчик</t>
+          <t>тахта кровать</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>175660</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>стелажи или стеллажи купить</t>
+          <t>купить кровать с ящиками и матрас</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>я хочу спать</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>78664</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>антресоль это</t>
+          <t>кровати диваны и матрасы</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>872</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>шифоньер это</t>
+          <t>односпальные кровати и матрасы</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>854</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>в гардеробах оборудуют места исходя из площади</t>
+          <t>кровать и матрас сайт</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>851</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>сервант это</t>
+          <t>орматек кровать</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -6034,61 +6643,496 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>как выбрать удобную мебель для балкона</t>
+          <t>кровать и матрас 160х200</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>786</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>стелаж или стеллаж как правильно</t>
+          <t>детские кровати и матрасы</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>751</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>шифонер или шифоньер как правильно написать</t>
+          <t>хочу спать</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>149668</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>мебелировка</t>
+          <t>купить кровать с матрасом и механизмом</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>638</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>купить кровать с подъемным механизмом и матрасом</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>диван раскладной на кухню со спальным местом</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>размеры кроватей и матрасов</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>купить недорогие кровати и матрасы</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>магазин кроватей и матрасов</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>деньги не спят</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>18851</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>кровать с подъемным механизмом и матрасом 160х200</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>спальная мебель</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7260</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>детские кровати с матрасом и ящиками</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>кровати и матрасы цена</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>кровать и матрас москве</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>диван кровать и ортопедическим матрасом</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>пастель или постель</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>купить матрас 160х200 и кровать</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>мебель кровати и матрасы</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>спальные кровати и матрасы</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>кровати и матрасы каталог и цены</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>кровать и матрас аскона</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>орматек кровать купить</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1807</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>кровати и матрасы отзывы</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>кровать диван с ящиками и матрасом</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>матрас двуспальный и кровать</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>купить кровать и матрас в москве</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ортопедическая кровать и матрас</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>кровати и матрасы официальный сайт</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>мягкие матрасы и кровати</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>матрасы и основания кроватей</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>кровать с изголовьем и матрасом</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>кровать односпальная с ящиками и матрасом</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
   </sheetData>
